--- a/sampleprojects/CorporateTax/excel/states/TX_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/TX_corp.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="154">
   <si>
     <t>DT: Determine TX Filing Requirement</t>
   </si>
@@ -79,7 +79,7 @@
     <t>Total revenue below $1.23M no-tax-due threshold; result.tx_total_revenue &lt; result.tx_no_tax_due_threshold</t>
   </si>
   <si>
-    <t>result.tx_total_revenue &lt; result.tx_no_tax_due_threshold</t>
+    <t>tx_result.total_revenue &lt; tx_result.no_tax_due_threshold</t>
   </si>
   <si>
     <t>ACTIONS: COMMENTS</t>
@@ -91,7 +91,7 @@
     <t>Physical presence but below threshold - no tax due; No tax due - total revenue below $1.23M threshold</t>
   </si>
   <si>
-    <t>set result.tx_qualifies_for_no_tax_due = true; set result.tx_franchise_tax = 0.0; set apportionment.state_tax = 0.0; add "TX franchise tax: No tax due (revenue below $1.23M threshold). Reference: TX Tax Code 171.002(d)(2)" to job.audit_trail;</t>
+    <t>set tx_result.qualifies_for_no_tax_due = true; set tx_result.franchise_tax = 0.0; set apportionment.state_tax = 0.0; add "TX franchise tax: No tax due (revenue below $1.23M threshold). Reference: TX Tax Code 171.002(d)(2)" to job.audit_trail;</t>
   </si>
   <si>
     <t>X</t>
@@ -100,19 +100,19 @@
     <t>Physical nexus established - franchise tax calculation required</t>
   </si>
   <si>
-    <t>set result.tx_qualifies_for_no_tax_due = false; add "TX franchise tax filing required due to physical presence. Reference: TX Tax Code 171.001" to job.audit_trail;</t>
+    <t>set tx_result.qualifies_for_no_tax_due = false; add "TX franchise tax filing required due to physical presence. Reference: TX Tax Code 171.001" to job.audit_trail;</t>
   </si>
   <si>
     <t>Economic nexus established - franchise tax calculation required; TX franchise tax filing required due to economic nexus ($500K threshold)</t>
   </si>
   <si>
-    <t>set result.tx_qualifies_for_no_tax_due = false; add "TX franchise tax filing required due to economic nexus ($500K TX receipts). Reference: TX Tax Code 171.0001(a)(1)" to job.audit_trail;</t>
+    <t>set tx_result.qualifies_for_no_tax_due = false; add "TX franchise tax filing required due to economic nexus ($500K TX receipts). Reference: TX Tax Code 171.0001(a)(1)" to job.audit_trail;</t>
   </si>
   <si>
     <t>No nexus - no filing required; No Texas nexus - no filing requirement</t>
   </si>
   <si>
-    <t>set result.tx_qualifies_for_no_tax_due = true; set result.tx_franchise_tax = 0.0; set apportionment.state_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments; add "No TX nexus - no filing required. Any estimated payments would be refunded." to job.audit_trail;</t>
+    <t>set tx_result.qualifies_for_no_tax_due = true; set tx_result.franchise_tax = 0.0; set apportionment.state_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments; add "No TX nexus - no filing required. Any estimated payments would be refunded." to job.audit_trail;</t>
   </si>
   <si>
     <t>DT: Determine TX Deduction Method</t>
@@ -127,37 +127,37 @@
     <t>Has nexus and above no-tax-due threshold; result.tx_qualifies_for_no_tax_due == false</t>
   </si>
   <si>
-    <t>result.tx_qualifies_for_no_tax_due == false</t>
+    <t>tx_result.qualifies_for_no_tax_due == false</t>
   </si>
   <si>
     <t>COGS is greater than compensation</t>
   </si>
   <si>
-    <t>result.tx_cogs &gt; result.tx_compensation</t>
+    <t>tx_result.cogs &gt; tx_result.compensation</t>
   </si>
   <si>
     <t>No nexus or below threshold - deduction method not applicable; No franchise tax due - deduction method not applicable</t>
   </si>
   <si>
-    <t>set result.tx_deduction_method = "none"; set result.tx_margin_deduction = 0.0; add "No TX franchise tax due - deduction method not applicable." to job.audit_trail;</t>
+    <t>set tx_result.deduction_method = "none"; set tx_result.margin_deduction = 0.0; add "No TX franchise tax due - deduction method not applicable." to job.audit_trail;</t>
   </si>
   <si>
     <t>Use 70% of revenue deduction; 70% of revenue provides largest deduction (simplified method)</t>
   </si>
   <si>
-    <t>set result.tx_deduction_method = "70_percent"; set result.tx_margin_deduction = result.tx_total_revenue * 0.70; add "TX franchise tax: Using 70% of revenue deduction method. Reference: TX Tax Code 171.1012(f)" to job.audit_trail;</t>
+    <t>set tx_result.deduction_method = "70_percent"; set tx_result.margin_deduction = tx_result.total_revenue * 0.70; add "TX franchise tax: Using 70% of revenue deduction method. Reference: TX Tax Code 171.1012(f)" to job.audit_trail;</t>
   </si>
   <si>
     <t>Use COGS deduction</t>
   </si>
   <si>
-    <t>set result.tx_deduction_method = "cogs"; set result.tx_margin_deduction = result.tx_cogs; add "TX franchise tax: Using COGS deduction method. Reference: TX Tax Code 171.1012(i)" to job.audit_trail;</t>
+    <t>set tx_result.deduction_method = "cogs"; set tx_result.margin_deduction = tx_result.cogs; add "TX franchise tax: Using COGS deduction method. Reference: TX Tax Code 171.1012(i)" to job.audit_trail;</t>
   </si>
   <si>
     <t>Use compensation deduction</t>
   </si>
   <si>
-    <t>set result.tx_deduction_method = "compensation"; set result.tx_margin_deduction = result.tx_compensation; add "TX franchise tax: Using compensation deduction method. Reference: TX Tax Code 171.1012(f)" to job.audit_trail;</t>
+    <t>set tx_result.deduction_method = "compensation"; set tx_result.margin_deduction = tx_result.compensation; add "TX franchise tax: Using compensation deduction method. Reference: TX Tax Code 171.1012(f)" to job.audit_trail;</t>
   </si>
   <si>
     <t>DT: Calculate TX Margin</t>
@@ -172,25 +172,25 @@
     <t>Qualifies for E-Z computation ($20M or less in revenue)</t>
   </si>
   <si>
-    <t>result.tx_total_revenue &lt;= 20000000.0</t>
+    <t>tx_result.total_revenue &lt;= 20000000.0</t>
   </si>
   <si>
     <t>No nexus or below threshold - no margin calculation; No franchise tax due - margin calculation not applicable</t>
   </si>
   <si>
-    <t>set result.tx_taxable_margin = 0.0; set result.tx_apportioned_margin = 0.0; add "No TX franchise tax due - margin calculation not applicable." to job.audit_trail;</t>
+    <t>set tx_result.taxable_margin = 0.0; set tx_result.apportioned_margin = 0.0; add "No TX franchise tax due - margin calculation not applicable." to job.audit_trail;</t>
   </si>
   <si>
     <t>E-Z Computation option available; Calculate margin - E-Z computation available ($20M or less)</t>
   </si>
   <si>
-    <t>set result.tx_qualifies_for_ez_computation = true; set result.tx_taxable_margin = the maximum of (result.tx_total_revenue - result.tx_margin_deduction) and (0.0); set result.tx_apportioned_margin = result.tx_taxable_margin * apportionment.apportionment_factor; add "TX margin calculated. E-Z computation available. Reference: TX Tax Code 171.1016" to job.audit_trail;</t>
+    <t>set tx_result.qualifies_for_ez_computation = true; set tx_result.taxable_margin = the maximum of (tx_result.total_revenue - tx_result.margin_deduction) and (0.0); set tx_result.apportioned_margin = tx_result.taxable_margin * apportionment.apportionment_factor; add "TX margin calculated. E-Z computation available. Reference: TX Tax Code 171.1016" to job.audit_trail;</t>
   </si>
   <si>
     <t>Standard margin calculation (no E-Z); Calculate margin - standard method (revenue exceeds $20M)</t>
   </si>
   <si>
-    <t>set result.tx_qualifies_for_ez_computation = false; set result.tx_taxable_margin = the maximum of (result.tx_total_revenue - result.tx_margin_deduction) and (0.0); set result.tx_apportioned_margin = result.tx_taxable_margin * apportionment.apportionment_factor; add "TX margin calculated using standard method. Reference: TX Tax Code 171.101" to job.audit_trail;</t>
+    <t>set tx_result.qualifies_for_ez_computation = false; set tx_result.taxable_margin = the maximum of (tx_result.total_revenue - tx_result.margin_deduction) and (0.0); set tx_result.apportioned_margin = tx_result.taxable_margin * apportionment.apportionment_factor; add "TX margin calculated using standard method. Reference: TX Tax Code 171.101" to job.audit_trail;</t>
   </si>
   <si>
     <t>DT: Calculate TX Franchise Tax</t>
@@ -205,49 +205,49 @@
     <t>Has positive apportioned margin</t>
   </si>
   <si>
-    <t>result.tx_apportioned_margin &gt; 0</t>
+    <t>tx_result.apportioned_margin &gt; 0</t>
   </si>
   <si>
     <t>Elects to use E-Z computation method; result.tx_qualifies_for_ez_computation == true</t>
   </si>
   <si>
-    <t>result.tx_qualifies_for_ez_computation == true</t>
+    <t>tx_result.qualifies_for_ez_computation == true</t>
   </si>
   <si>
     <t>Primarily engaged in retail or wholesale trade</t>
   </si>
   <si>
-    <t>result.tx_is_retail_wholesale == true</t>
+    <t>tx_result.is_retail_wholesale == true</t>
   </si>
   <si>
     <t>No nexus or below threshold - no franchise tax; No Texas franchise tax due</t>
   </si>
   <si>
-    <t>set result.tx_franchise_tax = 0.0; set apportionment.state_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments; add "No TX franchise tax due. Any estimated payments will be refunded. Reference: TX Tax Code 171.002(d)(2)" to job.audit_trail;</t>
+    <t>set tx_result.franchise_tax = 0.0; set apportionment.state_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments; add "No TX franchise tax due. Any estimated payments will be refunded. Reference: TX Tax Code 171.002(d)(2)" to job.audit_trail;</t>
   </si>
   <si>
     <t>E-Z Computation (simplified method); TX franchise tax using E-Z computation (0.575%)</t>
   </si>
   <si>
-    <t>set result.tx_franchise_tax = (the maximum of (result.tx_total_revenue - result.tx_no_tax_due_threshold) and (0.0)) * result.tx_ez_computation_rate * apportionment.apportionment_factor; set result.tx_franchise_tax = the maximum of (result.tx_franchise_tax - apportionment.state_credits) and (0.0); set apportionment.state_tax = result.tx_franchise_tax; set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax; add "TX franchise tax: E-Z computation. (Revenue - $1.23M) × 0.575%. NOT an income tax. Reference: TX Tax Code 171.1016" to job.audit_trail;</t>
+    <t>set tx_result.franchise_tax = (the maximum of (tx_result.total_revenue - tx_result.no_tax_due_threshold) and (0.0)) * tx_result.ez_computation_rate * apportionment.apportionment_factor; set tx_result.franchise_tax = the maximum of (tx_result.franchise_tax - apportionment.state_credits) and (0.0); set apportionment.state_tax = tx_result.franchise_tax; set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax; add "TX franchise tax: E-Z computation. (Revenue - $1.23M) × 0.575%. NOT an income tax. Reference: TX Tax Code 171.1016" to job.audit_trail;</t>
   </si>
   <si>
     <t>Retail/wholesale reduced rate (0.375%); TX franchise tax at reduced retail/wholesale rate</t>
   </si>
   <si>
-    <t>set result.tx_margin_tax_rate = 0.00375; set result.tx_franchise_tax = result.tx_apportioned_margin * result.tx_margin_tax_rate; set result.tx_franchise_tax = the maximum of (result.tx_franchise_tax - apportionment.state_credits) and (0.0); set apportionment.state_tax = result.tx_franchise_tax; set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax; add "TX franchise tax: Retail/wholesale rate 0.375%. NOT an income tax. Reference: TX Tax Code 171.002(b)" to job.audit_trail;</t>
+    <t>set tx_result.margin_tax_rate = 0.00375; set tx_result.franchise_tax = tx_result.apportioned_margin * tx_result.margin_tax_rate; set tx_result.franchise_tax = the maximum of (tx_result.franchise_tax - apportionment.state_credits) and (0.0); set apportionment.state_tax = tx_result.franchise_tax; set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax; add "TX franchise tax: Retail/wholesale rate 0.375%. NOT an income tax. Reference: TX Tax Code 171.002(b)" to job.audit_trail;</t>
   </si>
   <si>
     <t>Standard rate (0.75%); TX franchise tax at standard rate</t>
   </si>
   <si>
-    <t>set result.tx_margin_tax_rate = 0.0075; set result.tx_franchise_tax = result.tx_apportioned_margin * result.tx_margin_tax_rate; set result.tx_franchise_tax = the maximum of (result.tx_franchise_tax - apportionment.state_credits) and (0.0); set apportionment.state_tax = result.tx_franchise_tax; set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax; add "TX franchise tax: Standard rate 0.75%. NOT an income tax. Reference: TX Tax Code 171.002(a)" to job.audit_trail;</t>
+    <t>set tx_result.margin_tax_rate = 0.0075; set tx_result.franchise_tax = tx_result.apportioned_margin * tx_result.margin_tax_rate; set tx_result.franchise_tax = the maximum of (tx_result.franchise_tax - apportionment.state_credits) and (0.0); set apportionment.state_tax = tx_result.franchise_tax; set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax; add "TX franchise tax: Standard rate 0.75%. NOT an income tax. Reference: TX Tax Code 171.002(a)" to job.audit_trail;</t>
   </si>
   <si>
     <t>No apportioned margin - no franchise tax; No TX franchise tax due - zero or negative margin</t>
   </si>
   <si>
-    <t>set result.tx_franchise_tax = 0.0; set apportionment.state_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments; add "No TX franchise tax due - zero or negative margin. No loss carryforward. Reference: TX Tax Code 171.101" to job.audit_trail;</t>
+    <t>set tx_result.franchise_tax = 0.0; set apportionment.state_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments; add "No TX franchise tax due - zero or negative margin. No loss carryforward. Reference: TX Tax Code 171.101" to job.audit_trail;</t>
   </si>
   <si>
     <t>DT: Calculate TX Income Adjustments</t>
@@ -325,10 +325,10 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>apportionment</t>
-  </si>
-  <si>
-    <t>(8 attributes)</t>
+    <t>tx_apportionment</t>
+  </si>
+  <si>
+    <t>(4 attributes)</t>
   </si>
   <si>
     <t>apportionment_formula</t>
@@ -358,36 +358,12 @@
     <t>Texas economic nexus: $500,000 in Texas receipts (NOT the federal $100K standard)</t>
   </si>
   <si>
-    <t>state_additions</t>
+    <t>state_tax_rate</t>
   </si>
   <si>
     <t>0.0</t>
   </si>
   <si>
-    <t>Not applicable - Texas has no income tax</t>
-  </si>
-  <si>
-    <t>state_code</t>
-  </si>
-  <si>
-    <t>TX</t>
-  </si>
-  <si>
-    <t>Texas state code</t>
-  </si>
-  <si>
-    <t>state_credits</t>
-  </si>
-  <si>
-    <t>Texas franchise tax credits (film, enterprise zone, R&amp;D, etc.)</t>
-  </si>
-  <si>
-    <t>state_subtractions</t>
-  </si>
-  <si>
-    <t>state_tax_rate</t>
-  </si>
-  <si>
     <t>Texas has NO corporate income tax (franchise tax is calculated separately)</t>
   </si>
   <si>
@@ -403,40 +379,37 @@
     <t>Texas does not use transaction count threshold</t>
   </si>
   <si>
-    <t>result</t>
+    <t>tx_result</t>
   </si>
   <si>
     <t>(14 attributes)</t>
   </si>
   <si>
-    <t>tx_apportioned_margin</t>
+    <t>apportioned_margin</t>
   </si>
   <si>
     <t>Margin apportioned to Texas based on receipts</t>
   </si>
   <si>
-    <t>tx_cogs</t>
+    <t>cogs</t>
   </si>
   <si>
     <t>Texas COGS for margin tax calculation (optional deduction method)</t>
   </si>
   <si>
-    <t>tx_compensation</t>
+    <t>compensation</t>
   </si>
   <si>
     <t>Texas compensation (wages and benefits) for margin tax calculation (optional deduction method)</t>
   </si>
   <si>
-    <t>tx_deduction_method</t>
-  </si>
-  <si>
-    <t>cogs</t>
+    <t>deduction_method</t>
   </si>
   <si>
     <t>Method used to calculate margin: cogs, compensation, or 70_percent (taxpayer selects most beneficial)</t>
   </si>
   <si>
-    <t>tx_ez_computation_rate</t>
+    <t>ez_computation_rate</t>
   </si>
   <si>
     <t>0.00575</t>
@@ -445,13 +418,13 @@
     <t>E-Z computation rate (0.575% of revenue over $1.23M threshold)</t>
   </si>
   <si>
-    <t>tx_franchise_tax</t>
+    <t>franchise_tax</t>
   </si>
   <si>
     <t>Texas franchise tax liability (NOT an income tax)</t>
   </si>
   <si>
-    <t>tx_is_retail_wholesale</t>
+    <t>is_retail_wholesale</t>
   </si>
   <si>
     <t>boolean</t>
@@ -463,13 +436,13 @@
     <t>Business primarily engaged in retail or wholesale (qualifies for 0.375% rate)</t>
   </si>
   <si>
-    <t>tx_margin_deduction</t>
+    <t>margin_deduction</t>
   </si>
   <si>
     <t>Amount deducted from revenue based on selected method</t>
   </si>
   <si>
-    <t>tx_margin_tax_rate</t>
+    <t>margin_tax_rate</t>
   </si>
   <si>
     <t>0.0075</t>
@@ -478,7 +451,7 @@
     <t>TX franchise tax rate on taxable margin (0.75% for most businesses, 0.375% for retail/wholesale)</t>
   </si>
   <si>
-    <t>tx_no_tax_due_threshold</t>
+    <t>no_tax_due_threshold</t>
   </si>
   <si>
     <t>1230000.0</t>
@@ -487,25 +460,25 @@
     <t>Texas no tax due threshold ($1.23M in revenue for 2025)</t>
   </si>
   <si>
-    <t>tx_qualifies_for_ez_computation</t>
+    <t>qualifies_for_ez_computation</t>
   </si>
   <si>
     <t>Qualifies for Texas E-Z computation ($20M revenue or less)</t>
   </si>
   <si>
-    <t>tx_qualifies_for_no_tax_due</t>
+    <t>qualifies_for_no_tax_due</t>
   </si>
   <si>
     <t>Total revenue below $1.23M threshold - no franchise tax due</t>
   </si>
   <si>
-    <t>tx_taxable_margin</t>
+    <t>taxable_margin</t>
   </si>
   <si>
     <t>Taxable margin after deduction (revenue minus COGS or compensation)</t>
   </si>
   <si>
-    <t>tx_total_revenue</t>
+    <t>total_revenue</t>
   </si>
   <si>
     <t>Total revenue for Texas franchise tax (gross receipts from all sources)</t>
@@ -4740,14 +4713,14 @@
       <c r="B7" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>104</v>
+      <c r="C7" s="11" t="s">
+        <v>116</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>14</v>
@@ -4756,7 +4729,7 @@
         <v>106</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>14</v>
@@ -4775,187 +4748,187 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="H8" s="16" t="s">
+      <c r="A8" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="B8" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="8" t="s">
+      <c r="D9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="8" t="s">
+      <c r="F9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>106</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M9" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M9" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="7" t="s">
+      <c r="D10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="7" t="s">
+      <c r="F10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>106</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M10" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M10" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>106</v>
       </c>
       <c r="H11" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="I11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M11" s="8" t="s">
+      <c r="I11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M11" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="C12" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="H12" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
+      <c r="I12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="s">
@@ -4971,7 +4944,7 @@
         <v>14</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>14</v>
@@ -4980,7 +4953,7 @@
         <v>106</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>14</v>
@@ -5003,7 +4976,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>109</v>
@@ -5021,7 +4994,7 @@
         <v>106</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I14" s="8" t="s">
         <v>14</v>
@@ -5044,16 +5017,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>109</v>
+        <v>134</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>135</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>14</v>
@@ -5062,7 +5035,7 @@
         <v>106</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>14</v>
@@ -5085,16 +5058,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>104</v>
+        <v>138</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>14</v>
@@ -5103,7 +5076,7 @@
         <v>106</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I16" s="8" t="s">
         <v>14</v>
@@ -5126,7 +5099,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C17" s="11" t="s">
         <v>109</v>
@@ -5135,7 +5108,7 @@
         <v>14</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>14</v>
@@ -5144,7 +5117,7 @@
         <v>106</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I17" s="7" t="s">
         <v>14</v>
@@ -5167,7 +5140,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C18" s="11" t="s">
         <v>109</v>
@@ -5176,7 +5149,7 @@
         <v>14</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>14</v>
@@ -5185,7 +5158,7 @@
         <v>106</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="I18" s="8" t="s">
         <v>14</v>
@@ -5208,16 +5181,16 @@
         <v>14</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>14</v>
@@ -5226,7 +5199,7 @@
         <v>106</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>14</v>
@@ -5249,16 +5222,16 @@
         <v>14</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>109</v>
+        <v>148</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>135</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>14</v>
@@ -5267,7 +5240,7 @@
         <v>106</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I20" s="8" t="s">
         <v>14</v>
@@ -5290,7 +5263,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>109</v>
@@ -5299,7 +5272,7 @@
         <v>14</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>150</v>
+        <v>113</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>14</v>
@@ -5340,7 +5313,7 @@
         <v>14</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>153</v>
+        <v>113</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>14</v>
@@ -5349,7 +5322,7 @@
         <v>106</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I22" s="8" t="s">
         <v>14</v>
@@ -5364,170 +5337,6 @@
         <v>14</v>
       </c>
       <c r="M22" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="H23" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L23" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M23" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="H24" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K24" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L24" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M24" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="H25" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L25" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M25" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="H26" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K26" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M26" s="8" t="s">
         <v>14</v>
       </c>
     </row>
